--- a/data/sce_compartment_curation/2026_curated/mitochondrial_unassigned.xlsx
+++ b/data/sce_compartment_curation/2026_curated/mitochondrial_unassigned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B379"/>
+  <dimension ref="A1:B376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YJR073C</t>
+          <t>YHR171W</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YNL284C</t>
+          <t>YKR010C</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YDR343C</t>
+          <t>YDR039C</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YLR270W</t>
+          <t>YMR186W</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YOR168W</t>
+          <t>YLR270W</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YOR048C</t>
+          <t>YNL284C</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YDR150W</t>
+          <t>YBL111C</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YJR089W</t>
+          <t>YGL229C</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YOL129W</t>
+          <t>YPL202C</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YKL081W</t>
+          <t>YHR179W</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YPL033C</t>
+          <t>YJL131C</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YML026C</t>
+          <t>YGL020C</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YDL148C</t>
+          <t>YHR186C</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YHL032C</t>
+          <t>YDL240W</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YOR150W</t>
+          <t>YMR232W</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YJL096W</t>
+          <t>YAR035C-A</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YJL218W</t>
+          <t>YGL211W</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YHR004C</t>
+          <t>YBL080C</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YKL044W</t>
+          <t>YNR070W</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YDR342C</t>
+          <t>YLL060C</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YLR183C</t>
+          <t>YNL073W</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YPL040C</t>
+          <t>YDR124W</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YDR046C</t>
+          <t>YDR141C</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YCR008W</t>
+          <t>YGL023C</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Q0255</t>
+          <t>YBR081C</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YGR287C</t>
+          <t>YDL171C</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YML076C</t>
+          <t>YPL137C</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>YKL205W</t>
+          <t>YBL090W</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YOL021C</t>
+          <t>YML133C</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YIL129C</t>
+          <t>YPL167C</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YLR426W</t>
+          <t>YHR030C</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>YGL187C</t>
+          <t>YJR010W</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>YLR380W</t>
+          <t>YOR153W</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YGR052W</t>
+          <t>YEL037C</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YOR251C</t>
+          <t>YGL085W</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YFR004W</t>
+          <t>YOR206W</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YDL232W</t>
+          <t>YDR341C</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YGL195W</t>
+          <t>YDR477W</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YDL230W</t>
+          <t>YIL149C</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YML061C</t>
+          <t>YFR031C</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YLL007C</t>
+          <t>YGR285C</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>YKL033W</t>
+          <t>YLR426W</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YDR141C</t>
+          <t>YGR094W</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YLL036C</t>
+          <t>YOL129W</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YNL274C</t>
+          <t>YGL002W</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YDR132C</t>
+          <t>YPL033C</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YKL132C</t>
+          <t>YKL044W</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>YBR146W</t>
+          <t>Q0115</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YDR508C</t>
+          <t>YGR052W</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>YKL037W</t>
+          <t>YPL226W</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YLR346C</t>
+          <t>YEL067C</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YOR297C</t>
+          <t>Q0105</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YBR097W</t>
+          <t>YHR183W</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YDR027C</t>
+          <t>YNL227C</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Q0075</t>
+          <t>YIL162W</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YMR061W</t>
+          <t>YGR015C</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>YNL249C</t>
+          <t>YMR287C</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>YIL055C</t>
+          <t>YFL011W</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YDL182W</t>
+          <t>YPL196W</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YPL041C</t>
+          <t>YEL061C</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YGR015C</t>
+          <t>YMR192W</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YJR010W</t>
+          <t>YOR011W</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YMR224C</t>
+          <t>YHR091C</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YGL093W</t>
+          <t>YGL225W</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YLR132C</t>
+          <t>YPL105C</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YER076C</t>
+          <t>YDR450W</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>YDR305C</t>
+          <t>YPL096W</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YDR341C</t>
+          <t>YFR004W</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YKL203C</t>
+          <t>YDR150W</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YMR287C</t>
+          <t>YDR438W</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YBL016W</t>
+          <t>YPR184W</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YMR264W</t>
+          <t>YOL038W</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>YLR154W-C</t>
+          <t>YML026C</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YDL140C</t>
+          <t>YHR051W</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YNL195C</t>
+          <t>YNL274C</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YML007C-A</t>
+          <t>YJL109C</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>YNL077W</t>
+          <t>YDL015C</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YHR183W</t>
+          <t>YKR027W</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YNL213C</t>
+          <t>YLR442C</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YDR096W</t>
+          <t>YMR167W</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YMR221C</t>
+          <t>YBR146W</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YOR355W</t>
+          <t>YPL013C</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YML010W</t>
+          <t>YPL155C</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YDR505C</t>
+          <t>YHR189W</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>YMR031C</t>
+          <t>YLR335W</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YJL109C</t>
+          <t>YHR080C</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YHR050W</t>
+          <t>YCL005W</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YOR241W</t>
+          <t>YNL250W</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YLL040C</t>
+          <t>YPL036W</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YOR206W</t>
+          <t>YJR062C</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>YOR274W</t>
+          <t>YIL047C</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>YNR003C</t>
+          <t>YGL240W</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YHR030C</t>
+          <t>YML007C-A</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YGL104C</t>
+          <t>YHR050W</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>YFR024C-A</t>
+          <t>YBL016W</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>YDR301W</t>
+          <t>YPL148C</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YNL268W</t>
+          <t>YIL055C</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YBR200W</t>
+          <t>YML061C</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YPL069C</t>
+          <t>YDR268W</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YGL230C</t>
+          <t>YEL047C</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YEL034W</t>
+          <t>YIL066C</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YGR260W</t>
+          <t>YDR132C</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>YLR291C</t>
+          <t>YGL221C</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>YGR102C</t>
+          <t>YKL081W</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>YJL113W</t>
+          <t>YOR297C</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YPL105C</t>
+          <t>YER155C</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>YKL157W</t>
+          <t>YKR023W</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>YGR098C</t>
+          <t>YGL230C</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YJL094C</t>
+          <t>YNL195C</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>YPL082C</t>
+          <t>YNR003C</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>YER038W-A</t>
+          <t>YJL178C</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>YBR004C</t>
+          <t>YNR074C</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>YJL070C</t>
+          <t>YKR005C</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>YPR100W</t>
+          <t>YDL232W</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YOR386W</t>
+          <t>YGR260W</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>YAR035W</t>
+          <t>YHR067W</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>YEL061C</t>
+          <t>YPL082C</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>YBL111C</t>
+          <t>Q0255</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>YHL018W</t>
+          <t>YBR200W</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>YIL149C</t>
+          <t>YOL021C</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>YNL102W</t>
+          <t>YGR178C</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>YIL162W</t>
+          <t>YER164W</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>YGL008C</t>
+          <t>YLL040C</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YNL073W</t>
+          <t>YBR120C</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>YGR155W</t>
+          <t>YBR140C</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>YLR142W</t>
+          <t>YMR128W</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>YGL245W</t>
+          <t>YKR064W</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>YJL131C</t>
+          <t>YDR011W</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YOR070C</t>
+          <t>YBR229C</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YPL154C</t>
+          <t>YDL148C</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YDR538W</t>
+          <t>YJL096W</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YIL060W</t>
+          <t>YPL206C</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YPR097W</t>
+          <t>YDR263C</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YAR002C-A</t>
+          <t>YJL046W</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>YFR019W</t>
+          <t>YLR106C</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YAL062W</t>
+          <t>YNL102W</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YKR070W</t>
+          <t>YBR238C</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>YIL078W</t>
+          <t>YIL139C</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>YLR256W</t>
+          <t>YKL037W</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>YHR189W</t>
+          <t>YJL043W</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>YAL015C</t>
+          <t>YNL112W</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>YBR129C</t>
+          <t>YOR144C</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>YFR015C</t>
+          <t>YPL217C</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>YDR035W</t>
+          <t>YOR119C</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>YMR030W</t>
+          <t>YER115C</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YNL292W</t>
+          <t>YDL149W</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>YHR067W</t>
+          <t>YNR016C</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>YBR229C</t>
+          <t>YLR422W</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>YNL227C</t>
+          <t>YAL056W</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>YNR036C</t>
+          <t>YNR055C</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>YDL086W</t>
+          <t>YKL167C</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>YPR054W</t>
+          <t>YKL182W</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>YGR076C</t>
+          <t>YNL292W</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>YNL247W</t>
+          <t>YLR142W</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>YOR144C</t>
+          <t>YJL113W</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>YHR179W</t>
+          <t>YLR256W</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>YDR263C</t>
+          <t>YNL077W</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>YLR356W</t>
+          <t>YDL248W</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>YLR335W</t>
+          <t>YBR147W</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YMR207C</t>
+          <t>YKR094C</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>YDR326C</t>
+          <t>YNL063W</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>YOR384W</t>
+          <t>YLR370C</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YJR060W</t>
+          <t>YDL104C</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>YDR124W</t>
+          <t>YPL040C</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>YPL036W</t>
+          <t>YDL003W</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>YDR191W</t>
+          <t>YJR060W</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>YBR081C</t>
+          <t>YPR100W</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>YJR113C</t>
+          <t>YOR241W</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>YCR032W</t>
+          <t>YGL209W</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>YBR120C</t>
+          <t>YDR191W</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>YDR039C</t>
+          <t>YAR035W</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YLR305C</t>
+          <t>YAL015C</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>YBR136W</t>
+          <t>YLR087C</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>YER033C</t>
+          <t>YAL013W</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YHR080C</t>
+          <t>YJL070C</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>YGL209W</t>
+          <t>YNL249C</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Q0105</t>
+          <t>YFR024C-A</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>YEL037C</t>
+          <t>YAR002C-A</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>YDL040C</t>
+          <t>YEL050C</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>YGL197W</t>
+          <t>YML010W</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>YER181C</t>
+          <t>YNL318C</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>YMR078C</t>
+          <t>YDR419W</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>YER140W</t>
+          <t>YDL086W</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>YOR316C</t>
+          <t>YDR505C</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>YDL171C</t>
+          <t>YOL141W</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>YDR120C</t>
+          <t>YMR306W</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>YPL226W</t>
+          <t>YKL010C</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>YMR232W</t>
+          <t>YPR054W</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>YKR094C</t>
+          <t>YLL036C</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YGL002W</t>
+          <t>YJL218W</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>YPL096W</t>
+          <t>YOR246C</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>YML060W</t>
+          <t>YDL040C</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>YOR045W</t>
+          <t>YOR188W</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>YNR074C</t>
+          <t>YOR045W</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>YLL060C</t>
+          <t>YMR221C</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>YFR031C</t>
+          <t>YDR046C</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>YPL206C</t>
+          <t>YGL011C</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>YOL033W</t>
+          <t>YNL088W</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>YLR072W</t>
+          <t>YDL048C</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>YMR118C</t>
+          <t>YBR203W</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>YNL250W</t>
+          <t>YLR380W</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>YOL141W</t>
+          <t>YLR132C</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>YMR306W</t>
+          <t>YKR070W</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>YMR211W</t>
+          <t>YMR252C</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>YDR477W</t>
+          <t>YOR004W</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>YPL202C</t>
+          <t>YDR035W</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>YJL178C</t>
+          <t>YKR019C</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>YJR062C</t>
+          <t>YDL140C</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>YJR098C</t>
+          <t>YBR223C</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>YAL029C</t>
+          <t>YGR162W</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>YDL149W</t>
+          <t>YOR168W</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YLR106C</t>
+          <t>YPL069C</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>YGL120C</t>
+          <t>YFR019W</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>YKR064W</t>
+          <t>YDR115W</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>YLR383W</t>
+          <t>YNL213C</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>YHR155W</t>
+          <t>YDR049W</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Q0115</t>
+          <t>YNR036C</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>YLR368W</t>
+          <t>YER140W</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>YBR147W</t>
+          <t>YOL045W</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>YKL070W</t>
+          <t>YFR015C</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>YOR346W</t>
+          <t>YLR424W</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>YOR153W</t>
+          <t>YNL083W</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>YOL025W</t>
+          <t>YMR019W</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>YGL125W</t>
+          <t>YPL041C</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>YMR192W</t>
+          <t>YGL197W</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>YPL137C</t>
+          <t>YDL069C</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>YAL013W</t>
+          <t>YML060W</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>YER155C</t>
+          <t>YDR305C</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>YGR178C</t>
+          <t>YPR083W</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>YHR171W</t>
+          <t>YMR129W</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>YHR051W</t>
+          <t>YHR155W</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>YGL005C</t>
+          <t>YLR383W</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>YDL048C</t>
+          <t>YOR316C</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>YJL043W</t>
+          <t>YJR111C</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>YNR070W</t>
+          <t>YJR073C</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>YBR001C</t>
+          <t>YPR146C</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>YLR247C</t>
+          <t>YDL203C</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>YGR094W</t>
+          <t>YIL129C</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>YGR285C</t>
+          <t>YMR030W</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>YDL003W</t>
+          <t>YDL033C</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>YGL139W</t>
+          <t>YDR538W</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>YGL225W</t>
+          <t>YKL157W</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>YMR065W</t>
+          <t>YOR274W</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>YDR074W</t>
+          <t>YNL320W</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>YNL144C</t>
+          <t>YER093C-A</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>YPL283C</t>
+          <t>YDR077W</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>YLR305C</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>YOR011W</t>
+          <t>YKL132C</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>YDR011W</t>
+          <t>YNL144C</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>YDR419W</t>
+          <t>YER033C</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>YDR514C</t>
+          <t>YLL007C</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>YKL167C</t>
+          <t>YLR419W</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>YAR035C-A</t>
+          <t>YDR096W</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>YPR083W</t>
+          <t>YMR118C</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>YDL069C</t>
+          <t>YBR150C</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>YDL248W</t>
+          <t>YMR065W</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>YBR238C</t>
+          <t>YBR129C</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>YDL240W</t>
+          <t>YOR070C</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>YBR140C</t>
+          <t>YOR384W</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>YGR159C</t>
+          <t>YDL157C</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>YML133C</t>
+          <t>YIL078W</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>YNL083W</t>
+          <t>YKL033W</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>YGL011C</t>
+          <t>YKL205W</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>YNL112W</t>
+          <t>YPR099C</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>YDR438W</t>
+          <t>YGL073W</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>YPL217C</t>
+          <t>YGR169C</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>YBR150C</t>
+          <t>YGL125W</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>YDL033C</t>
+          <t>YDR326C</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>YPR048W</t>
+          <t>YLR154W-C</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>YOR188W</t>
+          <t>YHR004C</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>YOL045W</t>
+          <t>YKL203C</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>YPL196W</t>
+          <t>Q0075</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>YLR001C</t>
+          <t>YPR097W</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>YLR087C</t>
+          <t>YLR072W</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>YGR169C</t>
+          <t>YKL070W</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>YDR125C</t>
+          <t>YOR048C</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>YGL073W</t>
+          <t>YGL195W</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>YMR186W</t>
+          <t>YNL268W</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>YGL023C</t>
+          <t>YOL025W</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>YKL028W</t>
+          <t>YBL088C</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>YDL104C</t>
+          <t>YHL018W</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>YIL047C</t>
+          <t>YDR514C</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>YBL080C</t>
+          <t>YER181C</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>YIL139C</t>
+          <t>YOL033W</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>YKR027W</t>
+          <t>YNL247W</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>YDR077W</t>
+          <t>YGL187C</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>YLR165C</t>
+          <t>YER038W-A</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>YJL005W</t>
+          <t>YEL034W</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>YPR099C</t>
+          <t>YLR001C</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>YCL005W</t>
+          <t>YGL249W</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>YOR004W</t>
+          <t>YLR247C</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>YDR268W</t>
+          <t>YML076C</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>YGR162W</t>
+          <t>YHL035C</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>YDL022W</t>
+          <t>YLR183C</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>YOR119C</t>
+          <t>YGL169W</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>YKR019C</t>
+          <t>YBR001C</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>YMR167W</t>
+          <t>YGR287C</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>YDL157C</t>
+          <t>YPR095C</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YLR291C</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>YPR184W</t>
+          <t>YCR032W</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>YDL203C</t>
+          <t>YPR025C</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>YIL066C</t>
+          <t>YGR091W</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>YLR422W</t>
+          <t>YJL123C</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>YDR069C</t>
+          <t>YOR355W</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>YPL167C</t>
+          <t>YAL029C</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>YHL035C</t>
+          <t>YPR048W</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>YNR055C</t>
+          <t>YHL032C</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>YJL123C</t>
+          <t>YJL005W</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>YEL050C</t>
+          <t>YBR004C</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>YKR023W</t>
+          <t>YMR078C</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>YGR091W</t>
+          <t>YMR264W</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>YML021C</t>
+          <t>YCL064C</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>YER074W</t>
+          <t>YJL130C</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>YPL013C</t>
+          <t>YGL139W</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>YBL090W</t>
+          <t>YGR155W</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>YPR080W</t>
+          <t>YBR136W</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>YJL130C</t>
+          <t>YLR346C</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>YGL020C</t>
+          <t>YDR027C</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>YER093C-A</t>
+          <t>YJR089W</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>YMR129W</t>
+          <t>YPL154C</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>YNL063W</t>
+          <t>YOR251C</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>YOR246C</t>
+          <t>YDL022W</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>YOR191W</t>
+          <t>YDR125C</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>YGL211W</t>
+          <t>YLR454W</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>YER164W</t>
+          <t>YIL060W</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>YKR063C</t>
+          <t>YGL093W</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>YEL063C</t>
+          <t>YKR079C</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>YJL046W</t>
+          <t>YER015W</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>YPL155C</t>
+          <t>YOR386W</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>YHR091C</t>
+          <t>YOL081W</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>YGL169W</t>
+          <t>YDL230W</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>YKL010C</t>
+          <t>YOR150W</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>YAL056W</t>
+          <t>YDR120C</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>YGL229C</t>
+          <t>YER076C</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>YER015W</t>
+          <t>YGL245W</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>YMR252C</t>
+          <t>YGR098C</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>YLR370C</t>
+          <t>YOR191W</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>YKR005C</t>
+          <t>YMR224C</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>YDR115W</t>
+          <t>YKL028W</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>YFL011W</t>
+          <t>YGL063W</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>YHR106W</t>
+          <t>YMR061W</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>YGL221C</t>
+          <t>YJR113C</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>YBL088C</t>
+          <t>YDR069C</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>YNL088W</t>
+          <t>YAL062W</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>YKR079C</t>
+          <t>YEL063C</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>YMR019W</t>
+          <t>YDR508C</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>YDR049W</t>
+          <t>YGR159C</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>YEL067C</t>
+          <t>YMR207C</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>YBR203W</t>
+          <t>YLR368W</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>YPR095C</t>
+          <t>YER074W</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>YNL318C</t>
+          <t>YOR346W</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>YGL240W</t>
+          <t>YMR031C</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>YCL064C</t>
+          <t>YGL104C</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>YOL081W</t>
+          <t>YMR211W</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>YHR186C</t>
+          <t>YGR076C</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>YGL249W</t>
+          <t>YNL305C</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>YPR025C</t>
+          <t>YGL005C</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>YPR146C</t>
+          <t>YPL283C</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>YEL047C</t>
+          <t>YLR165C</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>YLR419W</t>
+          <t>YCR008W</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>YLR454W</t>
+          <t>YDR074W</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>YNR016C</t>
+          <t>YBR097W</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>YKL182W</t>
+          <t>YDL182W</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>YKR010C</t>
+          <t>YDR301W</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>YLR442C</t>
+          <t>YPR080W</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>YGL063W</t>
+          <t>YGL151W</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>YGL085W</t>
+          <t>YKR063C</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>YMR128W</t>
+          <t>YJR098C</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>YBR223C</t>
+          <t>YGR102C</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>YGL151W</t>
+          <t>YHR106W</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>YPL148C</t>
+          <t>YLR356W</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>YDR450W</t>
+          <t>YML021C</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>YDL015C</t>
+          <t>YJL094C</t>
         </is>
       </c>
     </row>
@@ -4181,37 +4181,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>YJR111C</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="n">
-        <v>375</v>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>YOL038W</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="1" t="n">
-        <v>376</v>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>YLR424W</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="1" t="n">
-        <v>377</v>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>YER115C</t>
+          <t>YGL120C</t>
         </is>
       </c>
     </row>
